--- a/docs/ARM.xlsx
+++ b/docs/ARM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EitanKrimer\Documents\university\ADSS\ADSS_Group_Y\docs\spec\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taoma\Downloads\תיכון ותכנון מערכות\ADSS_Group_Y\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAAB8A9D-C85D-46D8-8A5D-2F6A409DCB27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22AC8D47-5B03-4F14-94EC-E82C123BEC08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="1800" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-60" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ARM" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="85">
   <si>
     <t>ID</t>
   </si>
@@ -551,36 +551,6 @@
     <r>
       <rPr>
         <sz val="16"/>
-        <color theme="5" tint="0.39997558519241921"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Site</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>:
-- ID
-- Site type (Supplier or Branch)
-- site object FK
-- contact phone
-- contact name
-- site address
-- Recorded weight at site</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">The System must follow this format for </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
         <color rgb="FF00B0F0"/>
         <rFont val="Arial"/>
         <family val="2"/>
@@ -604,148 +574,6 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">For any Transport in the System, a </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="5" tint="-0.249977111117893"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Transport</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> should have:
-- Transport ID
-- planned datetime of transport
-- status (pending, started, done, done with issues)
-- Truck ID (FK to link to the </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FFE90505"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>actual truck</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">)
-- Driver ID (FK to link to the actual </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="7" tint="-0.499984740745262"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>driver</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">)
-- source - List of </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="5" tint="0.39997558519241921"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Site</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">(s) ID(s) (FKs)
-- destination - List of </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="5" tint="0.39997558519241921"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Site</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">(s) ID(s) (FKs)
-- List of </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Transport Issue Log</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> ID(s) (FK)
-- List of </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="0" tint="-0.34998626667073579"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>TransportRoutes</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> ID(s) (Fk)
-- actual start datetime
-- actual end datetime</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t xml:space="preserve">For any </t>
     </r>
     <r>
@@ -1982,7 +1810,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> have to Print the next drive for driver</t>
+      <t xml:space="preserve"> have to Print transport drives for driver - by Transport ID</t>
     </r>
   </si>
   <si>
@@ -1992,21 +1820,47 @@
     <r>
       <rPr>
         <sz val="16"/>
+        <color theme="9" tint="-0.249977111117893"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>System</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> have to show all the </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="2" tint="-0.749992370372631"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">TransportAreas </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">in the </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
         <color theme="9"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
       <t>System</t>
     </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> have to Print transport drives for driver - by Transport ID</t>
-    </r>
   </si>
   <si>
     <r>
@@ -2028,24 +1882,271 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve"> have to have show all the </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="5"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Transport</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> in the </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="9"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>System</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="9" tint="-0.249977111117893"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>System</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> have to show the TransportArea by ID</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="9"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>System</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> have to show </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>truck</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> by its ID</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="9"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>System</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> have to show all the  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>trucks</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> in the </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="9"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>System</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="9"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>System</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> have to show </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="7" tint="-0.249977111117893"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>drivers</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> by its ID</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="9"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>System</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> have to show </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>branch</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> by its ID</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="9"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>System</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve"> have to show all the </t>
     </r>
     <r>
       <rPr>
         <sz val="16"/>
-        <color theme="2" tint="-0.749992370372631"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">TransportAreas </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">in the </t>
+        <color theme="7" tint="-0.249977111117893"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>drivers</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> in the </t>
     </r>
     <r>
       <rPr>
@@ -2064,7 +2165,7 @@
     <r>
       <rPr>
         <sz val="16"/>
-        <color theme="9" tint="-0.249977111117893"/>
+        <color theme="9"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
@@ -2077,7 +2178,409 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> have to have show all the </t>
+      <t xml:space="preserve"> have to show  all the </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>branch</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> in the </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="9"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>System</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">F </t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="9"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>System</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> have to show gui for handle all the models</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="9"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>System</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> have to load/unload by the chioce of the </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>user</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> mock values (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>only</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> for this version)</t>
+    </r>
+  </si>
+  <si>
+    <t>Transport Managar</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>How to define the transport manager?</t>
+  </si>
+  <si>
+    <t>Trucks  weight</t>
+  </si>
+  <si>
+    <t>who and how to insert the weight to the system?</t>
+  </si>
+  <si>
+    <t>Transport area</t>
+  </si>
+  <si>
+    <t>who is the responsiable to define the transports areas?</t>
+  </si>
+  <si>
+    <t>TransportIssue</t>
+  </si>
+  <si>
+    <t>how to define in which cases we use unload trucks, etc.</t>
+  </si>
+  <si>
+    <t>on which cases we should cancel the transport</t>
+  </si>
+  <si>
+    <t>DONE</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The System must follow this format for </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="5" tint="0.39997558519241921"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>APhysicalSite</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">:
+- ID
+- Site name
+- Site address
+- Site phone
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Branch </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>inheritance from that</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">For any Transport in the System, a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="5" tint="-0.249977111117893"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Transport</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> should have:
+- Transport ID
+- planned datetime of transport
+- status (pending, started, done, done with issues)
+- Truck ID (FK to link to the </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFE90505"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>actual truck</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">)
+- Driver ID (FK to link to the actual </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="7" tint="-0.499984740745262"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>driver</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">)
+- source - List of </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="5" tint="0.39997558519241921"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>APhysicalSite</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">(s) ID(s) (FKs)
+- destination - List of </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="5" tint="0.39997558519241921"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>APhysicalSite</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">(s) ID(s) (FKs)
+- List of </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Transport Issue Log</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> ID(s) (FK)
+- List of </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="0" tint="-0.34998626667073579"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>TransportRoutes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> ID(s) (Fk)
+- actual start datetime
+- actual end datetime</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The System must follow this format for </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="8" tint="-0.499984740745262"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>TransportAreas</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>:
+- ID
+-area name (string)</t>
+    </r>
+  </si>
+  <si>
+    <t>DONE (SUPPORT ONLY USER)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="9"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>system</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> must check if there is at least one available </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FFFFC000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Driver</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> by time and date to start the </t>
     </r>
     <r>
       <rPr>
@@ -2088,24 +2591,6 @@
       </rPr>
       <t>Transport</t>
     </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> in the </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color theme="9"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>System</t>
-    </r>
   </si>
   <si>
     <r>
@@ -2114,43 +2599,20 @@
     <r>
       <rPr>
         <sz val="16"/>
-        <color theme="9" tint="-0.249977111117893"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>System</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> have to show the TransportArea by ID</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">The </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color theme="9"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>System</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> have to allow to Unstart </t>
+        <color rgb="FF92D050"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>system</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> must check if there is at least one available Stocker by date and time to start the </t>
     </r>
     <r>
       <rPr>
@@ -2161,424 +2623,20 @@
       </rPr>
       <t>Transport</t>
     </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color theme="1" tint="0.14999847407452621"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Transport's route</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">The </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color theme="9"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>System</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> have to show </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>truck</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> by its ID</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">The </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color theme="9"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>System</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> have to show all the  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>trucks</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> in the </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color theme="9"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>System</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">The </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color theme="9"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>System</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> have to show </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color theme="7" tint="-0.249977111117893"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>drivers</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> by its ID</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">The </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color theme="9"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>System</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> have to show </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>branch</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> by its ID</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">The </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color theme="9"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>System</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> have to show all the </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color theme="7" tint="-0.249977111117893"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>drivers</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> in the </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color theme="9"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>System</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">The </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color theme="9"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>System</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> have to show  all the </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>branch</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> in the </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color theme="9"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>System</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">F </t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">The </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color theme="9"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>System</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> have to show gui for handle all the models</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">The </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color theme="9"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>System</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> have to load/unload by the chioce of the </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF7030A0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>user</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> mock values (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>only</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> for this version)</t>
-    </r>
-  </si>
-  <si>
-    <t>Transport Managar</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
-    <t>How to define the transport manager?</t>
-  </si>
-  <si>
-    <t>Trucks  weight</t>
-  </si>
-  <si>
-    <t>who and how to insert the weight to the system?</t>
-  </si>
-  <si>
-    <t>Transport area</t>
-  </si>
-  <si>
-    <t>who is the responsiable to define the transports areas?</t>
-  </si>
-  <si>
-    <t>TransportIssue</t>
-  </si>
-  <si>
-    <t>how to define in which cases we use unload trucks, etc.</t>
-  </si>
-  <si>
-    <t>on which cases we should cancel the transport</t>
+  </si>
+  <si>
+    <t>The system must synchornize with Employ system that drivers will be one to one with employ table in Employ system</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="37" x14ac:knownFonts="1">
+  <fonts count="40" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -2597,7 +2655,7 @@
     <font>
       <sz val="16"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -2803,6 +2861,24 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color theme="8" tint="-0.499984740745262"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FF92D050"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FFFFC000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -2908,7 +2984,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
@@ -2963,9 +3039,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3255,17 +3328,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H76"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="21" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:G75"/>
+  <sheetFormatPr defaultColWidth="9.09765625" defaultRowHeight="20.399999999999999" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="2"/>
-    <col min="2" max="2" width="15.42578125" style="2" customWidth="1"/>
+    <col min="1" max="1" width="9.09765625" style="2"/>
+    <col min="2" max="2" width="15.3984375" style="2" customWidth="1"/>
     <col min="3" max="3" width="10" style="2" customWidth="1"/>
-    <col min="4" max="4" width="43.5703125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="12.140625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="9.140625" style="2"/>
-    <col min="7" max="7" width="26.28515625" style="2" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="2"/>
+    <col min="4" max="4" width="43.59765625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="12.09765625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="9.09765625" style="2"/>
+    <col min="7" max="7" width="26.296875" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.09765625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3300,7 +3373,7 @@
       <c r="F2" s="13"/>
       <c r="G2" s="13"/>
     </row>
-    <row r="3" spans="1:7" ht="121.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="123" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>1</v>
       </c>
@@ -3320,10 +3393,10 @@
         <v>7</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="101.25" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="102.6" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <f>A3+1</f>
         <v>2</v>
@@ -3344,10 +3417,10 @@
         <v>7</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="162" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="163.19999999999999" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <f>A4+1</f>
         <v>3</v>
@@ -3368,12 +3441,12 @@
         <v>7</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>14</v>
+        <v>77</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="207.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
-        <f t="shared" ref="A6:A37" si="0">A5+1</f>
+        <f t="shared" ref="A6:A38" si="0">A5+1</f>
         <v>4</v>
       </c>
       <c r="B6" s="3" t="s">
@@ -3392,10 +3465,10 @@
         <v>7</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="178.15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="178.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -3416,7 +3489,7 @@
         <v>7</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>14</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="198.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -3431,7 +3504,7 @@
         <v>13</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>27</v>
+        <v>78</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>6</v>
@@ -3440,10 +3513,10 @@
         <v>7</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="226.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="226.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -3455,7 +3528,7 @@
         <v>13</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>6</v>
@@ -3464,10 +3537,10 @@
         <v>7</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="343.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="343.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <f>A9+1</f>
         <v>8</v>
@@ -3479,7 +3552,7 @@
         <v>13</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>29</v>
+        <v>79</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>6</v>
@@ -3488,10 +3561,10 @@
         <v>7</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="142.15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="343.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>9</v>
       </c>
@@ -3502,19 +3575,19 @@
         <v>13</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F11" s="9" t="s">
+      <c r="F11" s="3" t="s">
         <v>7</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="60.75" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="142.19999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>10</v>
       </c>
@@ -3524,22 +3597,21 @@
       <c r="C12" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>16</v>
+      <c r="D12" s="7" t="s">
+        <v>28</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F12" s="3" t="s">
+      <c r="F12" s="9" t="s">
         <v>7</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="101.25" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="61.2" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
-        <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="B13" s="3" t="s">
@@ -3549,7 +3621,7 @@
         <v>13</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>6</v>
@@ -3558,10 +3630,10 @@
         <v>7</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="81" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="102" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -3569,23 +3641,23 @@
       <c r="B14" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="8" t="s">
-        <v>15</v>
+      <c r="C14" s="3" t="s">
+        <v>13</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="60.75" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="61.2" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -3597,44 +3669,45 @@
         <v>15</v>
       </c>
       <c r="D15" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="61.2" x14ac:dyDescent="0.25">
+      <c r="A16" s="3">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D16" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E15" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="64.150000000000006" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="8">
-        <v>14</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>44</v>
-      </c>
       <c r="E16" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="64.150000000000006" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="64.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="8">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>12</v>
@@ -3643,10 +3716,10 @@
         <v>15</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>7</v>
@@ -3655,9 +3728,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="60.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="64.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="8">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>12</v>
@@ -3669,7 +3742,7 @@
         <v>34</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>7</v>
@@ -3678,9 +3751,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="60.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="61.2" x14ac:dyDescent="0.25">
       <c r="A19" s="8">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>12</v>
@@ -3689,7 +3762,7 @@
         <v>15</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>6</v>
@@ -3698,253 +3771,253 @@
         <v>7</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="60.75" x14ac:dyDescent="0.25">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="61.2" x14ac:dyDescent="0.25">
       <c r="A20" s="8">
+        <v>17</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="61.2" x14ac:dyDescent="0.25">
+      <c r="A21" s="8">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C20" s="3" t="s">
+      <c r="B21" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="E20" s="3" t="s">
+      <c r="D21" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E21" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F20" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="81" x14ac:dyDescent="0.25">
-      <c r="A21" s="8">
+      <c r="F21" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="81.599999999999994" x14ac:dyDescent="0.25">
+      <c r="A22" s="8">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C21" s="3" t="s">
+      <c r="B22" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C22" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D21" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="E21" s="3" t="s">
+      <c r="D22" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="E22" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F21" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="60.75" x14ac:dyDescent="0.25">
-      <c r="A22" s="8">
+      <c r="F22" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="61.2" x14ac:dyDescent="0.25">
+      <c r="A23" s="8">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C22" s="3" t="s">
+      <c r="B23" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D22" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="E22" s="3" t="s">
+      <c r="D23" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="E23" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F22" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="60.75" x14ac:dyDescent="0.25">
-      <c r="A23" s="8">
+      <c r="F23" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="61.2" x14ac:dyDescent="0.25">
+      <c r="A24" s="8">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C23" s="3" t="s">
+      <c r="B24" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D23" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="E23" s="3" t="s">
+      <c r="D24" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="E24" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F23" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="60.75" x14ac:dyDescent="0.25">
-      <c r="A24" s="8">
+      <c r="F24" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="61.2" x14ac:dyDescent="0.25">
+      <c r="A25" s="8">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C24" s="3" t="s">
+      <c r="B25" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C25" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D24" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="E24" s="3" t="s">
+      <c r="D25" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="E25" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F24" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="60.75" x14ac:dyDescent="0.25">
-      <c r="A25" s="8">
+      <c r="F25" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="61.2" x14ac:dyDescent="0.25">
+      <c r="A26" s="8">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C25" s="3" t="s">
+      <c r="B26" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D25" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="E25" s="3" t="s">
+      <c r="D26" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="E26" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F25" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="60.75" x14ac:dyDescent="0.25">
-      <c r="A26" s="8">
+      <c r="F26" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="61.2" x14ac:dyDescent="0.25">
+      <c r="A27" s="8">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C26" s="3" t="s">
+      <c r="B27" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C27" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D26" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="E26" s="3" t="s">
+      <c r="D27" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E27" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F26" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="40.5" x14ac:dyDescent="0.25">
-      <c r="A27" s="8">
+      <c r="F27" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="40.799999999999997" x14ac:dyDescent="0.25">
+      <c r="A28" s="8">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C27" s="3" t="s">
+      <c r="B28" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C28" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D27" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="E27" s="3" t="s">
+      <c r="D28" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="E28" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F27" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="40.5" x14ac:dyDescent="0.25">
-      <c r="A28" s="8">
+      <c r="F28" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="40.799999999999997" x14ac:dyDescent="0.25">
+      <c r="A29" s="8">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C28" s="3" t="s">
+      <c r="B29" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C29" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D28" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="E28" s="3" t="s">
+      <c r="D29" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="E29" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F28" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="40.5" x14ac:dyDescent="0.25">
-      <c r="A29" s="8">
+      <c r="F29" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="40.799999999999997" x14ac:dyDescent="0.25">
+      <c r="A30" s="8">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D29" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="60.75" x14ac:dyDescent="0.25">
-      <c r="A30" s="8">
-        <v>29</v>
-      </c>
       <c r="B30" s="3" t="s">
         <v>12</v>
       </c>
@@ -3952,7 +4025,7 @@
         <v>15</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>6</v>
@@ -3961,12 +4034,12 @@
         <v>7</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="60.75" x14ac:dyDescent="0.25">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="61.2" x14ac:dyDescent="0.25">
       <c r="A31" s="8">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>12</v>
@@ -3975,7 +4048,7 @@
         <v>15</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>6</v>
@@ -3987,9 +4060,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="60.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" ht="61.2" x14ac:dyDescent="0.25">
       <c r="A32" s="8">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>12</v>
@@ -3998,7 +4071,7 @@
         <v>15</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>6</v>
@@ -4010,9 +4083,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="141.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" ht="61.2" x14ac:dyDescent="0.25">
       <c r="A33" s="8">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>12</v>
@@ -4020,11 +4093,11 @@
       <c r="C33" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>17</v>
+      <c r="D33" s="8" t="s">
+        <v>50</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>7</v>
@@ -4033,107 +4106,106 @@
         <v>14</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="121.5" x14ac:dyDescent="0.25">
-      <c r="A34" s="3">
+    <row r="34" spans="1:7" ht="142.80000000000001" x14ac:dyDescent="0.25">
+      <c r="A34" s="8">
+        <v>32</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="122.4" x14ac:dyDescent="0.25">
+      <c r="A35" s="3">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="B34" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C34" s="3" t="s">
+      <c r="B35" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C35" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D34" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G34" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" ht="81" x14ac:dyDescent="0.25">
-      <c r="A35" s="3">
+      <c r="D35" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="61.2" x14ac:dyDescent="0.25">
+      <c r="A36" s="3">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
-      <c r="B35" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C35" s="3" t="s">
+      <c r="B36" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C36" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D35" s="3" t="s">
+      <c r="D36" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E35" s="3" t="s">
+      <c r="E36" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F35" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" ht="222.75" x14ac:dyDescent="0.25">
-      <c r="A36" s="3">
+      <c r="F36" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="225.6" x14ac:dyDescent="0.25">
+      <c r="A37" s="3">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
-      <c r="B36" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C36" s="3" t="s">
+      <c r="B37" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C37" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D36" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E36" s="3" t="s">
+      <c r="D37" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E37" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F36" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G36" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" ht="81" x14ac:dyDescent="0.25">
-      <c r="A37" s="3">
+      <c r="F37" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="61.2" x14ac:dyDescent="0.25">
+      <c r="A38" s="3">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="B37" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E37" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G37" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" ht="40.5" x14ac:dyDescent="0.25">
-      <c r="A38" s="3">
-        <f t="shared" ref="A38:A40" si="1">A37+1</f>
-        <v>37</v>
-      </c>
       <c r="B38" s="3" t="s">
         <v>12</v>
       </c>
@@ -4141,7 +4213,7 @@
         <v>15</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>6</v>
@@ -4150,62 +4222,62 @@
         <v>7</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" ht="60.75" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="40.799999999999997" x14ac:dyDescent="0.25">
       <c r="A39" s="3">
+        <f t="shared" ref="A39:A41" si="1">A38+1</f>
+        <v>37</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="40.799999999999997" x14ac:dyDescent="0.25">
+      <c r="A40" s="3">
         <f t="shared" si="1"/>
         <v>38</v>
       </c>
-      <c r="B39" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C39" s="3" t="s">
+      <c r="B40" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C40" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D39" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="E39" s="3" t="s">
+      <c r="D40" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="E40" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F39" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G39" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" ht="60.75" x14ac:dyDescent="0.25">
-      <c r="A40" s="3">
+      <c r="F40" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="40.799999999999997" x14ac:dyDescent="0.25">
+      <c r="A41" s="3">
         <f t="shared" si="1"/>
         <v>39</v>
       </c>
-      <c r="B40" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E40" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G40" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" ht="60.75" x14ac:dyDescent="0.25">
-      <c r="A41" s="3">
-        <f t="shared" ref="A41:A76" si="2">A40+1</f>
-        <v>40</v>
-      </c>
       <c r="B41" s="3" t="s">
         <v>12</v>
       </c>
@@ -4213,7 +4285,7 @@
         <v>15</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>6</v>
@@ -4222,38 +4294,38 @@
         <v>7</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" ht="60.75" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="40.799999999999997" x14ac:dyDescent="0.25">
       <c r="A42" s="3">
+        <f t="shared" ref="A42:A75" si="2">A41+1</f>
+        <v>40</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="61.2" x14ac:dyDescent="0.25">
+      <c r="A43" s="3">
         <f t="shared" si="2"/>
         <v>41</v>
       </c>
-      <c r="B42" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F42" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" ht="40.5" x14ac:dyDescent="0.25">
-      <c r="A43" s="3">
-        <f t="shared" si="2"/>
-        <v>42</v>
-      </c>
       <c r="B43" s="3" t="s">
         <v>12</v>
       </c>
@@ -4261,48 +4333,46 @@
         <v>15</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F43" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F43" s="10" t="s">
         <v>7</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H43" s="19"/>
-    </row>
-    <row r="44" spans="1:8" ht="60.75" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="61.2" x14ac:dyDescent="0.25">
       <c r="A44" s="3">
+        <v>42</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="61.2" x14ac:dyDescent="0.25">
+      <c r="A45" s="3">
         <f t="shared" si="2"/>
         <v>43</v>
       </c>
-      <c r="B44" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" ht="60.75" x14ac:dyDescent="0.25">
-      <c r="A45" s="3">
-        <f t="shared" si="2"/>
-        <v>44</v>
-      </c>
       <c r="B45" s="3" t="s">
         <v>12</v>
       </c>
@@ -4310,266 +4380,285 @@
         <v>15</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>7</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" ht="60.75" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="40.799999999999997" x14ac:dyDescent="0.25">
       <c r="A46" s="3">
+        <v>44</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="40.799999999999997" x14ac:dyDescent="0.25">
+      <c r="A47" s="3">
         <f t="shared" si="2"/>
         <v>45</v>
       </c>
-      <c r="B46" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C46" s="3" t="s">
+      <c r="B47" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C47" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D46" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="E46" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F46" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G46" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" ht="40.5" x14ac:dyDescent="0.25">
-      <c r="A47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="40.799999999999997" x14ac:dyDescent="0.25">
+      <c r="A48" s="3">
         <f t="shared" si="2"/>
         <v>46</v>
       </c>
-      <c r="B47" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C47" s="3" t="s">
+      <c r="B48" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C48" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E47" s="3" t="s">
+      <c r="D48" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="E48" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F47" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" ht="40.5" x14ac:dyDescent="0.25">
-      <c r="A48" s="3">
+      <c r="F48" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="40.799999999999997" x14ac:dyDescent="0.25">
+      <c r="A49" s="3">
         <f t="shared" si="2"/>
         <v>47</v>
       </c>
-      <c r="B48" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C48" s="3" t="s">
+      <c r="B49" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C49" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D48" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="E48" s="3" t="s">
+      <c r="D49" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E49" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F48" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G48" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" ht="40.5" x14ac:dyDescent="0.25">
-      <c r="A49" s="3">
+      <c r="F49" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="40.799999999999997" x14ac:dyDescent="0.25">
+      <c r="A50" s="3">
         <f t="shared" si="2"/>
         <v>48</v>
       </c>
-      <c r="B49" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C49" s="3" t="s">
+      <c r="B50" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C50" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D49" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="E49" s="3" t="s">
+      <c r="D50" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E50" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F49" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G49" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" ht="40.5" x14ac:dyDescent="0.25">
-      <c r="A50" s="3">
+      <c r="F50" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="40.799999999999997" x14ac:dyDescent="0.25">
+      <c r="A51" s="3">
         <f t="shared" si="2"/>
         <v>49</v>
       </c>
-      <c r="B50" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C50" s="3" t="s">
+      <c r="B51" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C51" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D50" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="E50" s="3" t="s">
+      <c r="D51" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E51" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F50" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G50" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" ht="40.5" x14ac:dyDescent="0.25">
-      <c r="A51" s="3">
+      <c r="F51" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" ht="40.799999999999997" x14ac:dyDescent="0.25">
+      <c r="A52" s="3">
         <f t="shared" si="2"/>
         <v>50</v>
       </c>
-      <c r="B51" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D51" s="3" t="s">
+      <c r="B52" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D52" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="E51" s="3" t="s">
+      <c r="E52" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F51" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G51" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" ht="40.5" x14ac:dyDescent="0.25">
-      <c r="A52" s="3">
+      <c r="F52" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="61.8" x14ac:dyDescent="0.25">
+      <c r="A53" s="3">
         <f t="shared" si="2"/>
         <v>51</v>
       </c>
-      <c r="B52" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D52" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="E52" s="3" t="s">
+      <c r="B53" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E53" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F52" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" ht="40.5" x14ac:dyDescent="0.25">
-      <c r="A53" s="3">
+      <c r="F53" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="81.599999999999994" x14ac:dyDescent="0.25">
+      <c r="A54" s="3">
         <f t="shared" si="2"/>
         <v>52</v>
       </c>
-      <c r="B53" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="D53" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="E53" s="3" t="s">
+      <c r="B54" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="E54" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F53" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G53" s="3" t="s">
+      <c r="F54" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G54" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="54" spans="1:7" ht="81" x14ac:dyDescent="0.25">
-      <c r="A54" s="3">
+    <row r="55" spans="1:7" ht="81.599999999999994" x14ac:dyDescent="0.25">
+      <c r="A55" s="3">
         <f t="shared" si="2"/>
         <v>53</v>
       </c>
-      <c r="B54" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C54" s="3" t="s">
+      <c r="B55" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C55" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D54" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="E54" s="3" t="s">
+      <c r="D55" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="E55" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F54" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G54" s="3" t="s">
+      <c r="F55" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G55" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A55" s="3">
+    <row r="56" spans="1:7" ht="81.599999999999994" x14ac:dyDescent="0.25">
+      <c r="A56" s="3">
         <f t="shared" si="2"/>
         <v>54</v>
       </c>
-      <c r="B55" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C55" s="3"/>
-      <c r="D55" s="3"/>
-      <c r="E55" s="3"/>
-      <c r="F55" s="3"/>
-      <c r="G55" s="3"/>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56" s="3">
-        <f t="shared" si="2"/>
-        <v>55</v>
-      </c>
       <c r="B56" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C56" s="3"/>
-      <c r="D56" s="3"/>
-      <c r="E56" s="3"/>
-      <c r="F56" s="3"/>
-      <c r="G56" s="3"/>
+      <c r="C56" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="3">
         <f t="shared" si="2"/>
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B57" s="3" t="s">
         <v>12</v>
@@ -4583,7 +4672,7 @@
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="3">
         <f t="shared" si="2"/>
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B58" s="3" t="s">
         <v>12</v>
@@ -4597,7 +4686,7 @@
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="3">
         <f t="shared" si="2"/>
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B59" s="3" t="s">
         <v>12</v>
@@ -4611,7 +4700,7 @@
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="3">
         <f t="shared" si="2"/>
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B60" s="3" t="s">
         <v>12</v>
@@ -4625,7 +4714,7 @@
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="3">
         <f t="shared" si="2"/>
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>12</v>
@@ -4639,7 +4728,7 @@
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="3">
         <f t="shared" si="2"/>
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>12</v>
@@ -4653,7 +4742,7 @@
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="3">
         <f t="shared" si="2"/>
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B63" s="3" t="s">
         <v>12</v>
@@ -4667,7 +4756,7 @@
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="3">
         <f t="shared" si="2"/>
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B64" s="3" t="s">
         <v>12</v>
@@ -4681,7 +4770,7 @@
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="3">
         <f t="shared" si="2"/>
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B65" s="3" t="s">
         <v>12</v>
@@ -4695,7 +4784,7 @@
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="3">
         <f t="shared" si="2"/>
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B66" s="3" t="s">
         <v>12</v>
@@ -4709,7 +4798,7 @@
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="3">
         <f t="shared" si="2"/>
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B67" s="3" t="s">
         <v>12</v>
@@ -4723,7 +4812,7 @@
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="3">
         <f t="shared" si="2"/>
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B68" s="3" t="s">
         <v>12</v>
@@ -4737,7 +4826,7 @@
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="3">
         <f t="shared" si="2"/>
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B69" s="3" t="s">
         <v>12</v>
@@ -4751,7 +4840,7 @@
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="3">
         <f t="shared" si="2"/>
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B70" s="3" t="s">
         <v>12</v>
@@ -4765,7 +4854,7 @@
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="3">
         <f t="shared" si="2"/>
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B71" s="3" t="s">
         <v>12</v>
@@ -4779,7 +4868,7 @@
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="3">
         <f t="shared" si="2"/>
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B72" s="3" t="s">
         <v>12</v>
@@ -4793,7 +4882,7 @@
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="3">
         <f t="shared" si="2"/>
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B73" s="3" t="s">
         <v>12</v>
@@ -4807,7 +4896,7 @@
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="3">
         <f t="shared" si="2"/>
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B74" s="3" t="s">
         <v>12</v>
@@ -4821,7 +4910,7 @@
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="3">
         <f t="shared" si="2"/>
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B75" s="3" t="s">
         <v>12</v>
@@ -4831,20 +4920,6 @@
       <c r="E75" s="3"/>
       <c r="F75" s="3"/>
       <c r="G75" s="3"/>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A76" s="3">
-        <f t="shared" si="2"/>
-        <v>75</v>
-      </c>
-      <c r="B76" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C76" s="3"/>
-      <c r="D76" s="3"/>
-      <c r="E76" s="3"/>
-      <c r="F76" s="3"/>
-      <c r="G76" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -4864,13 +4939,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6A548FC-132A-4BCF-B26C-A9E84109E40A}">
   <dimension ref="A1:D11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="30" customWidth="1"/>
-    <col min="3" max="3" width="34.7109375" customWidth="1"/>
+    <col min="3" max="3" width="34.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="21" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="20.399999999999999" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
         <v>11</v>
       </c>
@@ -4878,7 +4953,7 @@
       <c r="C1" s="18"/>
       <c r="D1" s="11"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -4895,55 +4970,55 @@
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="42" x14ac:dyDescent="0.25">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="40.799999999999997" x14ac:dyDescent="0.25">
       <c r="A4" s="6">
         <f>A3+1</f>
         <v>2</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D4" s="11"/>
     </row>
-    <row r="5" spans="1:4" ht="63" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" ht="61.2" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
         <f>A4+1</f>
         <v>3</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D5" s="11"/>
     </row>
-    <row r="6" spans="1:4" ht="63" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" ht="61.2" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
         <f>A5+1</f>
         <v>4</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D6" s="11"/>
     </row>
-    <row r="7" spans="1:4" ht="42" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" ht="40.799999999999997" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <v>5</v>
       </c>
@@ -4951,25 +5026,25 @@
         <v>12</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="21" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="20.399999999999999" x14ac:dyDescent="0.25">
       <c r="A8" s="4"/>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
     </row>
-    <row r="9" spans="1:4" ht="21" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" ht="20.399999999999999" x14ac:dyDescent="0.25">
       <c r="A9" s="4"/>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
     </row>
-    <row r="10" spans="1:4" ht="21" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" ht="20.399999999999999" x14ac:dyDescent="0.25">
       <c r="A10" s="4"/>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
     </row>
-    <row r="11" spans="1:4" ht="21" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" ht="20.399999999999999" x14ac:dyDescent="0.25">
       <c r="A11" s="4"/>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
